--- a/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92555453056</v>
+        <v>46157.93112710395</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93112710395</v>
+        <v>46157.93136549844</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93136549844</v>
+        <v>46157.93384089646</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93384089646</v>
+        <v>46157.93695856499</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93695856499</v>
+        <v>46158.28204986905</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28204986905</v>
+        <v>46158.29652381231</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29652381231</v>
+        <v>46158.29807570005</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29807570005</v>
+        <v>46158.33370508794</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33370508794</v>
+        <v>46158.37221787285</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37221787285</v>
+        <v>46158.3727562647</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
